--- a/bets.xlsx
+++ b/bets.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S112"/>
+  <dimension ref="A1:S117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6664,9 +6664,6 @@
         <v/>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-    </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -6721,13 +6718,270 @@
       <c r="M112" t="n">
         <v>30</v>
       </c>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
       <c r="O112">
         <f>IF(UPPER(N112)="W",(H112-1)*L112,IF(UPPER(N112)="L",-L112,""))</f>
         <v/>
       </c>
       <c r="P112">
         <f>IF(UPPER(N112)="W",(H112-1)*M112,IF(UPPER(N112)="L",-M112,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>basketball_nba_preseason</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers vs Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>h2h</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J114" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L114" t="n">
+        <v>20</v>
+      </c>
+      <c r="M114" t="n">
+        <v>8</v>
+      </c>
+      <c r="O114">
+        <f>IF(UPPER(N114)="W",(H114-1)*L114,IF(UPPER(N114)="L",-L114,""))</f>
+        <v/>
+      </c>
+      <c r="P114">
+        <f>IF(UPPER(N114)="W",(H114-1)*M114,IF(UPPER(N114)="L",-M114,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>soccer_argentina_primera_division</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Instituto de Córdoba vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Instituto de Córdoba</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>h2h</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J115" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L115" t="n">
+        <v>20</v>
+      </c>
+      <c r="M115" t="n">
+        <v>13</v>
+      </c>
+      <c r="O115">
+        <f>IF(UPPER(N115)="W",(H115-1)*L115,IF(UPPER(N115)="L",-L115,""))</f>
+        <v/>
+      </c>
+      <c r="P115">
+        <f>IF(UPPER(N115)="W",(H115-1)*M115,IF(UPPER(N115)="L",-M115,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>soccer_germany_bundesliga2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim vs 1. FC Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>h2h</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I116" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J116" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>20</v>
+      </c>
+      <c r="M116" t="n">
+        <v>10</v>
+      </c>
+      <c r="O116">
+        <f>IF(UPPER(N116)="W",(H116-1)*L116,IF(UPPER(N116)="L",-L116,""))</f>
+        <v/>
+      </c>
+      <c r="P116">
+        <f>IF(UPPER(N116)="W",(H116-1)*M116,IF(UPPER(N116)="L",-M116,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>soccer_saudi_arabia_pro_league</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Al-Kholood vs Al-Qadsiah</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Al-Kholood</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>h2h</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>6</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J117" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L117" t="n">
+        <v>20</v>
+      </c>
+      <c r="M117" t="n">
+        <v>4</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117">
+        <f>IF(UPPER(N117)="W",(H117-1)*L117,IF(UPPER(N117)="L",-L117,""))</f>
+        <v/>
+      </c>
+      <c r="P117">
+        <f>IF(UPPER(N117)="W",(H117-1)*M117,IF(UPPER(N117)="L",-M117,""))</f>
         <v/>
       </c>
     </row>
